--- a/pipeline/credit_rating/output/saigonratings_xhtn_20260923.xlsx
+++ b/pipeline/credit_rating/output/saigonratings_xhtn_20260923.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
@@ -620,7 +620,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
@@ -687,7 +687,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
@@ -750,7 +750,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
@@ -813,7 +813,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
@@ -880,7 +880,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
@@ -947,7 +947,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S80" s="1" t="n">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S81" s="1" t="n">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S82" s="1" t="n">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S83" s="1" t="n">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S84" s="1" t="n">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S85" s="1" t="n">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S86" s="1" t="n">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S87" s="1" t="n">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S88" s="1" t="n">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S89" s="1" t="n">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S90" s="1" t="n">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S91" s="1" t="n">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S92" s="1" t="n">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S93" s="1" t="n">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S94" s="1" t="n">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S95" s="1" t="n">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S96" s="1" t="n">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S97" s="1" t="n">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S98" s="1" t="n">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S99" s="1" t="n">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S100" s="1" t="n">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S101" s="1" t="n">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S102" s="1" t="n">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S103" s="1" t="n">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S104" s="1" t="n">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S105" s="1" t="n">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S106" s="1" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S107" s="1" t="n">
@@ -7795,7 +7795,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S108" s="1" t="n">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S109" s="1" t="n">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S110" s="1" t="n">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S111" s="1" t="n">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S112" s="1" t="n">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S113" s="1" t="n">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S114" s="1" t="n">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S115" s="1" t="n">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S116" s="1" t="n">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S117" s="1" t="n">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S118" s="1" t="n">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S119" s="1" t="n">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S120" s="1" t="n">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S121" s="1" t="n">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S122" s="1" t="n">
@@ -8800,7 +8800,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S123" s="1" t="n">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S124" s="1" t="n">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S125" s="1" t="n">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S126" s="1" t="n">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S127" s="1" t="n">
@@ -9135,7 +9135,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S128" s="1" t="n">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S129" s="1" t="n">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S130" s="1" t="n">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S131" s="1" t="n">
@@ -9403,7 +9403,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S132" s="1" t="n">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S133" s="1" t="n">
@@ -9537,7 +9537,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S134" s="1" t="n">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S135" s="1" t="n">
@@ -9675,7 +9675,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S136" s="1" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S137" s="1" t="n">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S138" s="1" t="n">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S139" s="1" t="n">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S140" s="1" t="n">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S141" s="1" t="n">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S142" s="1" t="n">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S143" s="1" t="n">
@@ -10219,7 +10219,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S144" s="1" t="n">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S145" s="1" t="n">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S146" s="1" t="n">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S147" s="1" t="n">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S148" s="1" t="n">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S149" s="1" t="n">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S150" s="1" t="n">
@@ -10688,7 +10688,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S151" s="1" t="n">
@@ -10755,7 +10755,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S152" s="1" t="n">
@@ -10822,7 +10822,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S153" s="1" t="n">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S154" s="1" t="n">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S155" s="1" t="n">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S156" s="1" t="n">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S157" s="1" t="n">
@@ -11157,7 +11157,7 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S158" s="1" t="n">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S159" s="1" t="n">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S160" s="1" t="n">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S161" s="1" t="n">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S162" s="1" t="n">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S163" s="1" t="n">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S164" s="1" t="n">
@@ -11626,7 +11626,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S165" s="1" t="n">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S166" s="1" t="n">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S167" s="1" t="n">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S168" s="1" t="n">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S169" s="1" t="n">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S170" s="1" t="n">
@@ -12028,7 +12028,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S171" s="1" t="n">
@@ -12095,7 +12095,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S172" s="1" t="n">
@@ -12162,7 +12162,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S173" s="1" t="n">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S174" s="1" t="n">
@@ -12296,7 +12296,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S175" s="1" t="n">
@@ -12363,7 +12363,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S176" s="1" t="n">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S177" s="1" t="n">
@@ -12497,7 +12497,7 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S178" s="1" t="n">
@@ -12564,7 +12564,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S179" s="1" t="n">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S180" s="1" t="n">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S181" s="1" t="n">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S182" s="1" t="n">
@@ -12832,7 +12832,7 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S183" s="1" t="n">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S184" s="1" t="n">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S185" s="1" t="n">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S186" s="1" t="n">
@@ -13100,7 +13100,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S187" s="1" t="n">
@@ -13167,7 +13167,7 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S188" s="1" t="n">
@@ -13234,7 +13234,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S189" s="1" t="n">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S190" s="1" t="n">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S191" s="1" t="n">
@@ -13435,7 +13435,7 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S192" s="1" t="n">
@@ -13506,7 +13506,7 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S193" s="1" t="n">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S194" s="1" t="n">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S195" s="1" t="n">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S196" s="1" t="n">
@@ -13774,7 +13774,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S197" s="1" t="n">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S198" s="1" t="n">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S199" s="1" t="n">
@@ -13975,7 +13975,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S200" s="1" t="n">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S201" s="1" t="n">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S202" s="1" t="n">
@@ -14176,7 +14176,7 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S203" s="1" t="n">
@@ -14243,7 +14243,7 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S204" s="1" t="n">
@@ -14310,7 +14310,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S205" s="1" t="n">
@@ -14377,7 +14377,7 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S206" s="1" t="n">
@@ -14444,7 +14444,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S207" s="1" t="n">
@@ -14511,7 +14511,7 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S208" s="1" t="n">
@@ -14578,7 +14578,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S209" s="1" t="n">
@@ -14645,7 +14645,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S210" s="1" t="n">
@@ -14712,7 +14712,7 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S211" s="1" t="n">
@@ -14779,7 +14779,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S212" s="1" t="n">
@@ -14846,7 +14846,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S213" s="1" t="n">
@@ -14913,7 +14913,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S214" s="1" t="n">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S215" s="1" t="n">
@@ -15047,7 +15047,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S216" s="1" t="n">
@@ -15114,7 +15114,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S217" s="1" t="n">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S218" s="1" t="n">
@@ -15248,7 +15248,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S219" s="1" t="n">
@@ -15315,7 +15315,7 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S220" s="1" t="n">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S221" s="1" t="n">
@@ -15449,7 +15449,7 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S222" s="1" t="n">
@@ -15516,7 +15516,7 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S223" s="1" t="n">
@@ -15583,7 +15583,7 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S224" s="1" t="n">
@@ -15650,7 +15650,7 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S225" s="1" t="n">
@@ -15717,7 +15717,7 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S226" s="1" t="n">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S227" s="1" t="n">
@@ -15851,7 +15851,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S228" s="1" t="n">
@@ -15918,7 +15918,7 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S229" s="1" t="n">
@@ -15985,7 +15985,7 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S230" s="1" t="n">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S231" s="1" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S232" s="1" t="n">
@@ -16186,7 +16186,7 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S233" s="1" t="n">
@@ -16253,7 +16253,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S234" s="1" t="n">
@@ -16320,7 +16320,7 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S235" s="1" t="n">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S236" s="1" t="n">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S237" s="1" t="n">
@@ -16521,7 +16521,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S238" s="1" t="n">
@@ -16588,7 +16588,7 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S239" s="1" t="n">
@@ -16655,7 +16655,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S240" s="1" t="n">
@@ -16722,7 +16722,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S241" s="1" t="n">
@@ -16789,7 +16789,7 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S242" s="1" t="n">
@@ -16856,7 +16856,7 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S243" s="1" t="n">
@@ -16923,7 +16923,7 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S244" s="1" t="n">
@@ -16990,7 +16990,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S245" s="1" t="n">
@@ -17057,7 +17057,7 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S246" s="1" t="n">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S247" s="1" t="n">
@@ -17191,7 +17191,7 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S248" s="1" t="n">
@@ -17258,7 +17258,7 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S249" s="1" t="n">
@@ -17325,7 +17325,7 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S250" s="1" t="n">
@@ -17392,7 +17392,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S251" s="1" t="n">
@@ -17459,7 +17459,7 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S252" s="1" t="n">
@@ -17526,7 +17526,7 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S253" s="1" t="n">
@@ -17593,7 +17593,7 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S254" s="1" t="n">
@@ -17660,7 +17660,7 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S255" s="1" t="n">
@@ -17727,7 +17727,7 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S256" s="1" t="n">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S257" s="1" t="n">
@@ -17861,7 +17861,7 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S258" s="1" t="n">
@@ -17928,7 +17928,7 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S259" s="1" t="n">
@@ -17995,7 +17995,7 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S260" s="1" t="n">
@@ -18062,7 +18062,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S261" s="1" t="n">
@@ -18129,7 +18129,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S262" s="1" t="n">
@@ -18196,7 +18196,7 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S263" s="1" t="n">
@@ -18263,7 +18263,7 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S264" s="1" t="n">
@@ -18330,7 +18330,7 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S265" s="1" t="n">
@@ -18397,7 +18397,7 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S266" s="1" t="n">
@@ -18464,7 +18464,7 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S267" s="1" t="n">
@@ -18531,7 +18531,7 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S268" s="1" t="n">
@@ -18598,7 +18598,7 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S269" s="1" t="n">
@@ -18665,7 +18665,7 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S270" s="1" t="n">
@@ -18732,7 +18732,7 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S271" s="1" t="n">
@@ -18799,7 +18799,7 @@
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S272" s="1" t="n">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S273" s="1" t="n">
@@ -18933,7 +18933,7 @@
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S274" s="1" t="n">
@@ -19000,7 +19000,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S275" s="1" t="n">
@@ -19067,7 +19067,7 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S276" s="1" t="n">
@@ -19134,7 +19134,7 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S277" s="1" t="n">
@@ -19201,7 +19201,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S278" s="1" t="n">
@@ -19268,7 +19268,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S279" s="1" t="n">
@@ -19335,7 +19335,7 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S280" s="1" t="n">
@@ -19402,7 +19402,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S281" s="1" t="n">
@@ -19469,7 +19469,7 @@
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S282" s="1" t="n">
@@ -19536,7 +19536,7 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S283" s="1" t="n">
@@ -19603,7 +19603,7 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S284" s="1" t="n">
@@ -19670,7 +19670,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S285" s="1" t="n">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S286" s="1" t="n">
@@ -19804,7 +19804,7 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S287" s="1" t="n">
@@ -19871,7 +19871,7 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S288" s="1" t="n">
@@ -19938,7 +19938,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S289" s="1" t="n">
@@ -20005,7 +20005,7 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S290" s="1" t="n">
@@ -20072,7 +20072,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S291" s="1" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S292" s="1" t="n">
@@ -20206,7 +20206,7 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S293" s="1" t="n">
@@ -20273,7 +20273,7 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S294" s="1" t="n">
@@ -20340,7 +20340,7 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S295" s="1" t="n">
@@ -20407,7 +20407,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S296" s="1" t="n">
@@ -20474,7 +20474,7 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S297" s="1" t="n">
@@ -20541,7 +20541,7 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S298" s="1" t="n">
@@ -20608,7 +20608,7 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S299" s="1" t="n">
@@ -20675,7 +20675,7 @@
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S300" s="1" t="n">
@@ -20742,7 +20742,7 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S301" s="1" t="n">
@@ -20809,7 +20809,7 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S302" s="1" t="n">
@@ -20876,7 +20876,7 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S303" s="1" t="n">
@@ -20943,7 +20943,7 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S304" s="1" t="n">
@@ -21010,7 +21010,7 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S305" s="1" t="n">
@@ -21077,7 +21077,7 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S306" s="1" t="n">
@@ -21144,7 +21144,7 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S307" s="1" t="n">
@@ -21211,7 +21211,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S308" s="1" t="n">
@@ -21278,7 +21278,7 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S309" s="1" t="n">
@@ -21345,7 +21345,7 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S310" s="1" t="n">
@@ -21412,7 +21412,7 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S311" s="1" t="n">
@@ -21479,7 +21479,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S312" s="1" t="n">
@@ -21546,7 +21546,7 @@
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S313" s="1" t="n">
@@ -21613,7 +21613,7 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S314" s="1" t="n">
@@ -21680,7 +21680,7 @@
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S315" s="1" t="n">
@@ -21747,7 +21747,7 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S316" s="1" t="n">
@@ -21814,7 +21814,7 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S317" s="1" t="n">
@@ -21881,7 +21881,7 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S318" s="1" t="n">
@@ -21948,7 +21948,7 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S319" s="1" t="n">
@@ -22015,7 +22015,7 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S320" s="1" t="n">
@@ -22082,7 +22082,7 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S321" s="1" t="n">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S322" s="1" t="n">
@@ -22216,7 +22216,7 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S323" s="1" t="n">
@@ -22283,7 +22283,7 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S324" s="1" t="n">
@@ -22350,7 +22350,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S325" s="1" t="n">
@@ -22417,7 +22417,7 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S326" s="1" t="n">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S327" s="1" t="n">
@@ -22551,7 +22551,7 @@
       </c>
       <c r="R328" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S328" s="1" t="n">
@@ -22602,7 +22602,7 @@
       </c>
       <c r="R329" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S329" t="inlineStr"/>
@@ -22651,7 +22651,7 @@
       </c>
       <c r="R330" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S330" t="inlineStr"/>
@@ -22700,7 +22700,7 @@
       </c>
       <c r="R331" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S331" t="inlineStr"/>
@@ -22749,7 +22749,7 @@
       </c>
       <c r="R332" t="inlineStr">
         <is>
-          <t>2026-09-23 08:48:36</t>
+          <t>2026-09-23 13:48:55</t>
         </is>
       </c>
       <c r="S332" t="inlineStr"/>
